--- a/doc/8.Calcul/Consomation Total.xlsx
+++ b/doc/8.Calcul/Consomation Total.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eduvaud-my.sharepoint.com/personal/py13jta_eduvaud_ch/Documents/00_Diplome/2510_RegulationChauffage/doc/8.Calcul/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="8_{6D37B1DA-F485-43C4-9A4C-41CF1B924667}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{796C7518-39F7-4B8B-B80A-8032D19E6C2B}"/>
+  <xr:revisionPtr revIDLastSave="45" documentId="8_{6D37B1DA-F485-43C4-9A4C-41CF1B924667}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F091ACFC-3786-460E-97BD-373A9D6C29F8}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2C036080-930E-4B79-8ED5-37F9184B695B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25560" windowHeight="21600" xr2:uid="{2C036080-930E-4B79-8ED5-37F9184B695B}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="31">
   <si>
     <t>Tension[V]</t>
   </si>
@@ -102,9 +102,6 @@
   </si>
   <si>
     <t>LED Power</t>
-  </si>
-  <si>
-    <t>74HC595PW,118 (min = 0 X, typ = 1 X, max = 4 X )</t>
   </si>
   <si>
     <t>ADG732BSUZ-REEL(min = 0 X, typ = 1 X, max = 4 X )</t>
@@ -578,7 +575,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -592,12 +589,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
@@ -605,13 +600,45 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -621,44 +648,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -668,12 +665,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -693,9 +684,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office 2013 – 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -733,7 +724,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -839,7 +830,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -981,7 +972,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -989,7 +980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4880068-6E37-4936-880D-425D7B9478EC}">
-  <dimension ref="E1:P33"/>
+  <dimension ref="E1:P32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
@@ -1003,7 +994,7 @@
   <sheetData>
     <row r="1" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F1" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G1" s="14" t="s">
         <v>0</v>
@@ -1011,7 +1002,7 @@
       <c r="H1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="25" t="s">
+      <c r="I1" s="22" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1022,11 +1013,11 @@
       <c r="G2" s="14">
         <v>24</v>
       </c>
-      <c r="H2" s="25">
+      <c r="H2" s="22">
         <f>I2/G2</f>
         <v>0.625</v>
       </c>
-      <c r="I2" s="25">
+      <c r="I2" s="22">
         <v>15</v>
       </c>
     </row>
@@ -1037,10 +1028,10 @@
       <c r="G3" s="14">
         <v>5</v>
       </c>
-      <c r="H3" s="25">
+      <c r="H3" s="22">
         <v>2.5</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="22">
         <f>G3*H3</f>
         <v>12.5</v>
       </c>
@@ -1052,40 +1043,40 @@
       <c r="G4" s="14">
         <v>3.3</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="22">
         <v>0.3</v>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="22">
         <f>G4*H4</f>
         <v>0.98999999999999988</v>
       </c>
     </row>
     <row r="5" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="42" t="s">
+      <c r="G6" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="H6" s="42">
+      <c r="H6" s="29">
         <v>24</v>
       </c>
-      <c r="I6" s="44" t="s">
+      <c r="I6" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="J6" s="45"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="M6" s="45"/>
-      <c r="N6" s="46"/>
+      <c r="J6" s="25"/>
+      <c r="K6" s="25"/>
+      <c r="L6" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="M6" s="25"/>
+      <c r="N6" s="26"/>
     </row>
     <row r="7" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F7" s="41"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="43"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="30"/>
+      <c r="H7" s="30"/>
       <c r="I7" s="4" t="s">
         <v>8</v>
       </c>
@@ -1106,11 +1097,11 @@
       </c>
     </row>
     <row r="8" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F8" s="34" t="s">
+      <c r="F8" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="35"/>
-      <c r="H8" s="36"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="33"/>
       <c r="I8" s="7" t="s">
         <v>19</v>
       </c>
@@ -1133,11 +1124,11 @@
       </c>
     </row>
     <row r="9" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F9" s="37" t="s">
+      <c r="F9" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="38"/>
-      <c r="H9" s="39"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="36"/>
       <c r="I9" s="10">
         <v>0</v>
       </c>
@@ -1159,64 +1150,64 @@
       </c>
     </row>
     <row r="10" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F10" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="27">
+      <c r="F10" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" s="38"/>
+      <c r="H10" s="39"/>
+      <c r="I10" s="24">
         <f>SUM(I8:I9)</f>
         <v>0</v>
       </c>
-      <c r="J10" s="22">
+      <c r="J10" s="20">
         <f>SUM(J8:J9)</f>
         <v>5.1460000000000004E-3</v>
       </c>
-      <c r="K10" s="22">
+      <c r="K10" s="20">
         <f>SUM(K8:K9)</f>
         <v>5.1460000000000004E-3</v>
       </c>
-      <c r="L10" s="22">
+      <c r="L10" s="20">
         <f>L8+L9</f>
         <v>0</v>
       </c>
-      <c r="M10" s="22">
+      <c r="M10" s="20">
         <f>M8+M9</f>
         <v>2.4344999999999999</v>
       </c>
-      <c r="N10" s="23">
+      <c r="N10" s="21">
         <f>N8+N9</f>
         <v>5.7775039999999995</v>
       </c>
-      <c r="O10" s="30"/>
-      <c r="P10" s="25"/>
+      <c r="O10" s="14"/>
+      <c r="P10" s="22"/>
     </row>
     <row r="12" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F13" s="50" t="s">
+      <c r="F13" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="G13" s="40" t="s">
+      <c r="G13" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="H13" s="42">
+      <c r="H13" s="29">
         <v>5</v>
       </c>
-      <c r="I13" s="44" t="s">
+      <c r="I13" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="J13" s="45"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="M13" s="45"/>
-      <c r="N13" s="46"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" s="25"/>
+      <c r="N13" s="26"/>
     </row>
     <row r="14" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F14" s="51"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="43"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="30"/>
       <c r="I14" s="10" t="s">
         <v>8</v>
       </c>
@@ -1237,40 +1228,40 @@
       </c>
     </row>
     <row r="15" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F15" s="34" t="s">
+      <c r="F15" s="31" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="35"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="17">
+      <c r="G15" s="32"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="15">
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="J15" s="18">
+      <c r="J15" s="16">
         <v>0.4</v>
       </c>
-      <c r="K15" s="18">
+      <c r="K15" s="16">
         <v>0.9</v>
       </c>
-      <c r="L15" s="18">
+      <c r="L15" s="16">
         <f t="shared" ref="L15:N19" si="0">$H$13*I15</f>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="M15" s="18">
+      <c r="M15" s="16">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="N15" s="19">
+      <c r="N15" s="17">
         <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
     </row>
     <row r="16" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F16" s="47" t="s">
+      <c r="F16" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="48"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="20">
+      <c r="G16" s="44"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="18">
         <v>0</v>
       </c>
       <c r="J16" s="1">
@@ -1293,12 +1284,12 @@
       </c>
     </row>
     <row r="17" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F17" s="47" t="s">
+      <c r="F17" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="G17" s="48"/>
-      <c r="H17" s="49"/>
-      <c r="I17" s="20">
+      <c r="G17" s="44"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="18">
         <v>0</v>
       </c>
       <c r="J17" s="1">
@@ -1321,12 +1312,12 @@
       </c>
     </row>
     <row r="18" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F18" s="47" t="s">
+      <c r="F18" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="G18" s="48"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="20">
+      <c r="G18" s="44"/>
+      <c r="H18" s="45"/>
+      <c r="I18" s="18">
         <v>0</v>
       </c>
       <c r="J18" s="1">
@@ -1351,12 +1342,12 @@
       </c>
     </row>
     <row r="19" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F19" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="48"/>
-      <c r="H19" s="49"/>
-      <c r="I19" s="20">
+      <c r="F19" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="44"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="18">
         <v>0</v>
       </c>
       <c r="J19" s="1">
@@ -1381,12 +1372,12 @@
       </c>
     </row>
     <row r="20" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F20" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="38"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="26" t="s">
+      <c r="F20" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="G20" s="35"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="23" t="s">
         <v>19</v>
       </c>
       <c r="J20" s="11" t="s">
@@ -1399,73 +1390,73 @@
         <v>0</v>
       </c>
       <c r="M20" s="11">
-        <f>M32</f>
-        <v>0.13439909999999999</v>
+        <f>M31</f>
+        <v>0.13413510000000001</v>
       </c>
       <c r="N20" s="12">
-        <f>N32</f>
-        <v>0.1356366</v>
+        <f>N31</f>
+        <v>0.13458059999999999</v>
       </c>
     </row>
     <row r="21" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F21" s="31" t="s">
-        <v>31</v>
-      </c>
-      <c r="G21" s="32"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="27">
+      <c r="F21" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="38"/>
+      <c r="H21" s="39"/>
+      <c r="I21" s="24">
         <f t="shared" ref="I21:N21" si="1">SUM(I15:I18)</f>
         <v>3.0000000000000001E-3</v>
       </c>
-      <c r="J21" s="22">
+      <c r="J21" s="20">
         <f t="shared" si="1"/>
         <v>0.46220000000000006</v>
       </c>
-      <c r="K21" s="22">
+      <c r="K21" s="20">
         <f t="shared" si="1"/>
         <v>1.1308</v>
       </c>
-      <c r="L21" s="22">
+      <c r="L21" s="20">
         <f t="shared" si="1"/>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="M21" s="22">
+      <c r="M21" s="20">
         <f t="shared" si="1"/>
         <v>2.3109999999999999</v>
       </c>
-      <c r="N21" s="23">
+      <c r="N21" s="21">
         <f t="shared" si="1"/>
         <v>5.6539999999999999</v>
       </c>
-      <c r="O21" s="30"/>
-      <c r="P21" s="25"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="22"/>
     </row>
     <row r="23" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="24" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F24" s="40" t="s">
+      <c r="F24" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="G24" s="40" t="s">
+      <c r="G24" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="H24" s="42">
+      <c r="H24" s="29">
         <v>3.3</v>
       </c>
-      <c r="I24" s="44" t="s">
+      <c r="I24" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="J24" s="45"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="45" t="s">
-        <v>25</v>
-      </c>
-      <c r="M24" s="45"/>
-      <c r="N24" s="46"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="M24" s="25"/>
+      <c r="N24" s="26"/>
     </row>
     <row r="25" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F25" s="41"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="43"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28"/>
+      <c r="H25" s="30"/>
       <c r="I25" s="10" t="s">
         <v>8</v>
       </c>
@@ -1486,71 +1477,71 @@
       </c>
     </row>
     <row r="26" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F26" s="34" t="s">
+      <c r="F26" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="G26" s="35"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="21">
-        <v>0</v>
-      </c>
-      <c r="J26" s="24">
+      <c r="G26" s="32"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="19">
+        <v>0</v>
+      </c>
+      <c r="J26" s="16">
         <f>0.000635</f>
         <v>6.3500000000000004E-4</v>
       </c>
-      <c r="K26" s="24">
+      <c r="K26" s="16">
         <f>0.00074</f>
         <v>7.3999999999999999E-4</v>
       </c>
-      <c r="L26" s="18">
-        <f>$H$13*I26</f>
-        <v>0</v>
-      </c>
-      <c r="M26" s="18">
-        <f t="shared" ref="M26:N31" si="2">$H$24*J26</f>
+      <c r="L26" s="16">
+        <f t="shared" ref="L26:L30" si="2">$H$13*I26</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="16">
+        <f t="shared" ref="M26:N30" si="3">$H$24*J26</f>
         <v>2.0955000000000001E-3</v>
       </c>
-      <c r="N26" s="19">
-        <f t="shared" si="2"/>
+      <c r="N26" s="17">
+        <f t="shared" si="3"/>
         <v>2.4419999999999997E-3</v>
       </c>
     </row>
     <row r="27" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F27" s="47" t="s">
+      <c r="F27" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="G27" s="48"/>
-      <c r="H27" s="49"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="45"/>
       <c r="I27" s="2">
         <v>0</v>
       </c>
-      <c r="J27" s="16">
+      <c r="J27" s="1">
         <f>0.000002</f>
         <v>1.9999999999999999E-6</v>
       </c>
-      <c r="K27" s="16">
+      <c r="K27" s="1">
         <f>0.000002</f>
         <v>1.9999999999999999E-6</v>
       </c>
       <c r="L27" s="1">
-        <f>$H$13*I27</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M27" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.5999999999999995E-6</v>
       </c>
       <c r="N27" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.5999999999999995E-6</v>
       </c>
     </row>
     <row r="28" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F28" s="34" t="s">
+      <c r="F28" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="G28" s="35"/>
-      <c r="H28" s="36"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="33"/>
       <c r="I28" s="7">
         <v>0</v>
       </c>
@@ -1563,24 +1554,24 @@
         <v>0.02</v>
       </c>
       <c r="L28" s="8">
-        <f>$H$13*I28</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M28" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.6000000000000003E-2</v>
       </c>
       <c r="N28" s="3">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
     <row r="29" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F29" s="37" t="s">
+      <c r="F29" s="34" t="s">
         <v>22</v>
       </c>
-      <c r="G29" s="38"/>
-      <c r="H29" s="39"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="36"/>
       <c r="I29" s="10">
         <v>0</v>
       </c>
@@ -1593,124 +1584,103 @@
         <v>0.02</v>
       </c>
       <c r="L29" s="11">
-        <f>$H$13*I29</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="M29" s="1">
+        <f t="shared" si="3"/>
+        <v>6.6000000000000003E-2</v>
+      </c>
+      <c r="N29" s="3">
+        <f t="shared" si="3"/>
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F30" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="G30" s="35"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="10">
+        <v>0</v>
+      </c>
+      <c r="J30" s="11">
+        <f>0.00001</f>
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="K30" s="11">
+        <f>4*0.00001</f>
+        <v>4.0000000000000003E-5</v>
+      </c>
+      <c r="L30" s="11">
         <f t="shared" si="2"/>
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="N29" s="3">
-        <f t="shared" si="2"/>
-        <v>6.6000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="6:16" x14ac:dyDescent="0.25">
-      <c r="F30" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="G30" s="48"/>
-      <c r="H30" s="49"/>
-      <c r="I30" s="2">
-        <v>0</v>
-      </c>
-      <c r="J30" s="16">
-        <f>0.00008</f>
-        <v>8.0000000000000007E-5</v>
-      </c>
-      <c r="K30" s="16">
-        <f>4*J30</f>
-        <v>3.2000000000000003E-4</v>
-      </c>
-      <c r="L30" s="1">
-        <f>$H$13*I30</f>
-        <v>0</v>
-      </c>
-      <c r="M30" s="1">
-        <f t="shared" si="2"/>
-        <v>2.6400000000000002E-4</v>
-      </c>
-      <c r="N30" s="3">
-        <f t="shared" si="2"/>
-        <v>1.0560000000000001E-3</v>
+        <v>0</v>
+      </c>
+      <c r="M30" s="11">
+        <f t="shared" si="3"/>
+        <v>3.3000000000000003E-5</v>
+      </c>
+      <c r="N30" s="12">
+        <f t="shared" si="3"/>
+        <v>1.3200000000000001E-4</v>
       </c>
     </row>
     <row r="31" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="F31" s="37" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G31" s="38"/>
       <c r="H31" s="39"/>
-      <c r="I31" s="10">
-        <v>0</v>
-      </c>
-      <c r="J31" s="28">
-        <f>0.00001</f>
-        <v>1.0000000000000001E-5</v>
-      </c>
-      <c r="K31" s="28">
-        <f>4*0.00001</f>
-        <v>4.0000000000000003E-5</v>
-      </c>
-      <c r="L31" s="11">
-        <f>$H$13*I31</f>
-        <v>0</v>
-      </c>
-      <c r="M31" s="11">
-        <f t="shared" si="2"/>
-        <v>3.3000000000000003E-5</v>
-      </c>
-      <c r="N31" s="12">
-        <f t="shared" si="2"/>
-        <v>1.3200000000000001E-4</v>
-      </c>
-    </row>
-    <row r="32" spans="6:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="F32" s="31" t="s">
-        <v>30</v>
-      </c>
-      <c r="G32" s="32"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="27">
-        <f t="shared" ref="I32:N32" si="3">SUM(I26:I31)</f>
-        <v>0</v>
-      </c>
-      <c r="J32" s="29">
-        <f t="shared" si="3"/>
-        <v>4.0726999999999999E-2</v>
-      </c>
-      <c r="K32" s="29">
-        <f t="shared" si="3"/>
-        <v>4.1102E-2</v>
-      </c>
-      <c r="L32" s="22">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M32" s="22">
-        <f t="shared" si="3"/>
-        <v>0.13439909999999999</v>
-      </c>
-      <c r="N32" s="23">
-        <f t="shared" si="3"/>
-        <v>0.1356366</v>
-      </c>
-      <c r="O32" s="30"/>
-      <c r="P32" s="25"/>
-    </row>
-    <row r="33" spans="6:14" x14ac:dyDescent="0.25">
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="15"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="15"/>
+      <c r="I31" s="24">
+        <f>SUM(I26:I30)</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="20">
+        <f>SUM(J26:J30)</f>
+        <v>4.0647000000000003E-2</v>
+      </c>
+      <c r="K31" s="20">
+        <f>SUM(K26:K30)</f>
+        <v>4.0781999999999999E-2</v>
+      </c>
+      <c r="L31" s="20">
+        <f>SUM(L26:L30)</f>
+        <v>0</v>
+      </c>
+      <c r="M31" s="20">
+        <f>SUM(M26:M30)</f>
+        <v>0.13413510000000001</v>
+      </c>
+      <c r="N31" s="21">
+        <f>SUM(N26:N30)</f>
+        <v>0.13458059999999999</v>
+      </c>
+      <c r="O31" s="14"/>
+      <c r="P31" s="22"/>
+    </row>
+    <row r="32" spans="6:16" x14ac:dyDescent="0.25">
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="31">
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F24:F25"/>
+    <mergeCell ref="G24:G25"/>
+    <mergeCell ref="H24:H25"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="G6:G7"/>
@@ -1727,22 +1697,6 @@
     <mergeCell ref="I13:K13"/>
     <mergeCell ref="L13:N13"/>
     <mergeCell ref="F26:H26"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F24:F25"/>
-    <mergeCell ref="G24:G25"/>
-    <mergeCell ref="H24:H25"/>
-    <mergeCell ref="I24:K24"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F32:H32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
